--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יניב רם - כוחה של אמונה</v>
+        <v>פרחי ירושלים - רני שב הביתה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409407&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409411&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יניב רם - כוחה של אמונה</v>
+        <v>פרחי ירושלים - רני שב הביתה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>זואי קפלן - סיפור אחר</v>
+        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409406&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409410&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-29</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>זואי קפלן - סיפור אחר</v>
+        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>גיל קדלר - נשכבה</v>
+        <v>סיימון גרידיש - חמש לפנות בוקר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409405&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409409&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-29</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>גיל קדלר - נשכבה</v>
+        <v>סיימון גרידיש - חמש לפנות בוקר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>גבריאל דמרי - מחרוזת קצב של פעם 2026</v>
+        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409404&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409408&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -583,126 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>גבריאל דמרי - מחרוזת קצב של פעם 2026</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אליקם בוטה - תהיה מאושר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409403&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אליקם בוטה - תהיה מאושר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אליה רומנו - הילד הקטן שלך</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409402&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אליה רומנו - הילד הקטן שלך</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אלחנן אלחדד - תנגן את זה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409401&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אלחנן אלחדד - תנגן את זה</v>
+        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרחי ירושלים - רני שב הביתה</v>
+        <v>מאור יפרח - ניסיתי מהלב 2</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409411&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409420&amp;sid=c7d448190c80f69daa71470781758b56</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרחי ירושלים - רני שב הביתה</v>
+        <v>מאור יפרח - ניסיתי מהלב 2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
+        <v>מאור יפרח - את כאן לתמיד</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409410&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409419&amp;sid=c7d448190c80f69daa71470781758b56</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
+        <v>מאור יפרח - את כאן לתמיד</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>סיימון גרידיש - חמש לפנות בוקר</v>
+        <v>מאור יפרח - אבא בשמיים</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409409&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409418&amp;sid=c7d448190c80f69daa71470781758b56</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>סיימון גרידיש - חמש לפנות בוקר</v>
+        <v>מאור יפרח - אבא בשמיים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
+        <v>יגל יובל שרעבי - אביר על סוס לבן</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409408&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409417&amp;sid=c7d448190c80f69daa71470781758b56</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,12 +583,164 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
+        <v>יגל יובל שרעבי - אביר על סוס לבן</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>גאנגשמאנג מארחים את דוד אלדר - דוקטור</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409416&amp;sid=c7d448190c80f69daa71470781758b56</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>גאנגשמאנג מארחים את דוד אלדר - דוקטור</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אורין כולב - הולכת לאיבוד</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409415&amp;sid=c7d448190c80f69daa71470781758b56</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אורין כולב - הולכת לאיבוד</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אוהד דוד לוי - ספטמבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409414&amp;sid=c7d448190c80f69daa71470781758b56</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אוהד דוד לוי - ספטמבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את יהודה גלילי - לכו נרננה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409413&amp;sid=c7d448190c80f69daa71470781758b56</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את יהודה גלילי - לכו נרננה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאור יפרח - ניסיתי מהלב 2</v>
+        <v>קובי ממן - סיגריה אחרונה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409420&amp;sid=c7d448190c80f69daa71470781758b56</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409423&amp;sid=66002cc5f41e639212beff12031784f0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-30</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאור יפרח - ניסיתי מהלב 2</v>
+        <v>קובי ממן - סיגריה אחרונה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מאור יפרח - את כאן לתמיד</v>
+        <v>נחמן עמרמי - כמה טוב בלב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409419&amp;sid=c7d448190c80f69daa71470781758b56</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409422&amp;sid=66002cc5f41e639212beff12031784f0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-30</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מאור יפרח - את כאן לתמיד</v>
+        <v>נחמן עמרמי - כמה טוב בלב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מאור יפרח - אבא בשמיים</v>
+        <v>מוטי שאלתיאל - ההילולה בתולאל</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409418&amp;sid=c7d448190c80f69daa71470781758b56</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409421&amp;sid=66002cc5f41e639212beff12031784f0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-30</v>
@@ -545,202 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מאור יפרח - אבא בשמיים</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>יגל יובל שרעבי - אביר על סוס לבן</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409417&amp;sid=c7d448190c80f69daa71470781758b56</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>יגל יובל שרעבי - אביר על סוס לבן</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>גאנגשמאנג מארחים את דוד אלדר - דוקטור</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409416&amp;sid=c7d448190c80f69daa71470781758b56</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>גאנגשמאנג מארחים את דוד אלדר - דוקטור</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אורין כולב - הולכת לאיבוד</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409415&amp;sid=c7d448190c80f69daa71470781758b56</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אורין כולב - הולכת לאיבוד</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אוהד דוד לוי - ספטמבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409414&amp;sid=c7d448190c80f69daa71470781758b56</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אוהד דוד לוי - ספטמבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את יהודה גלילי - לכו נרננה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409413&amp;sid=c7d448190c80f69daa71470781758b56</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את יהודה גלילי - לכו נרננה</v>
+        <v>מוטי שאלתיאל - ההילולה בתולאל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי ממן - סיגריה אחרונה</v>
+        <v>שי שלום - רק להיום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409423&amp;sid=66002cc5f41e639212beff12031784f0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409426&amp;sid=e152fc812c718c16af23893e38ed1407</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-30</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי ממן - סיגריה אחרונה</v>
+        <v>שי שלום - רק להיום</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נחמן עמרמי - כמה טוב בלב</v>
+        <v>שי שלום - מי ישיר לך</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409422&amp;sid=66002cc5f41e639212beff12031784f0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409425&amp;sid=e152fc812c718c16af23893e38ed1407</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-30</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נחמן עמרמי - כמה טוב בלב</v>
+        <v>שי שלום - מי ישיר לך</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מוטי שאלתיאל - ההילולה בתולאל</v>
+        <v>שי שלום - במיטה לבד</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409421&amp;sid=66002cc5f41e639212beff12031784f0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409424&amp;sid=e152fc812c718c16af23893e38ed1407</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-30</v>
@@ -545,7 +545,7 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מוטי שאלתיאל - ההילולה בתולאל</v>
+        <v>שי שלום - במיטה לבד</v>
       </c>
     </row>
   </sheetData>
